--- a/api/templates/export/routers/en.xlsx
+++ b/api/templates/export/routers/en.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25629"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\export\routers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\export\routers\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A03E937-20FF-4E61-BEE9-ED617B35BACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="480" windowWidth="20730" windowHeight="11760" tabRatio="815"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Routers" sheetId="1" r:id="rId1"/>
-    <sheet name="Error Codes" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -25,106 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Run-time error</t>
-  </si>
-  <si>
-    <t>The actual temperature has drifted too far away from the setpoint</t>
-  </si>
-  <si>
-    <t>The temperature difference exceeds the limit</t>
-  </si>
-  <si>
-    <t>The internal instrument temperature was out of range</t>
-  </si>
-  <si>
-    <t>Optic signal of from detector exceeded the limit</t>
-  </si>
-  <si>
-    <t>Detector dark signal exceeded the limit</t>
-  </si>
-  <si>
-    <t>The power supply was detected to be out of range</t>
-  </si>
-  <si>
-    <t>The measured temperature of the optical system was not within the acceptable range</t>
-  </si>
-  <si>
-    <t>A valve positioning error was detected at the end of the run</t>
-  </si>
-  <si>
-    <t>Operation terminated error</t>
-  </si>
-  <si>
-    <t>Module is already running a test while performing command</t>
-  </si>
-  <si>
-    <t>Motion of the syringe drive was not detected</t>
-  </si>
-  <si>
-    <t>Syringe pressure reading exceeds the protocol limit</t>
-  </si>
-  <si>
-    <t>Syringe pressure reading is below the protocol limit</t>
-  </si>
-  <si>
-    <t>Cartridge loading error</t>
-  </si>
-  <si>
-    <t>Unable to initialize pressure sensor</t>
-  </si>
-  <si>
-    <t>The digital temperature reading for Thermistor A/Thermistor B/Ambient Thermistor/Optic Thermistor was not within the acceptable range</t>
-  </si>
-  <si>
-    <t>The system was unable to find the valve home position</t>
-  </si>
-  <si>
-    <t>Attempt to load a cartridge while the door is still closed</t>
-  </si>
-  <si>
-    <t>Failed to get to desired temperature</t>
-  </si>
-  <si>
-    <t>The system failed to find the plunger home position</t>
-  </si>
-  <si>
-    <t>The ultrasonic horn could not be tuned properly</t>
-  </si>
-  <si>
-    <t>The optical signal from Detector did not reach the expected value</t>
-  </si>
-  <si>
-    <t>The cartridge integrity test failed</t>
-  </si>
-  <si>
-    <t>Self-test error</t>
-  </si>
-  <si>
-    <t>Cooling fan operation was not verified. Measured temperature exceeded the limit</t>
-  </si>
-  <si>
-    <t>Post-run analysis error</t>
-  </si>
-  <si>
-    <t>Probe check failed. Probe check value was above the maximum</t>
-  </si>
-  <si>
-    <t>Probe check failed. Probe check value was below the minimum</t>
-  </si>
-  <si>
-    <t>Signal loss detected in the amplification curve</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>&lt;name&gt;</t>
   </si>
@@ -157,12 +58,15 @@
   </si>
   <si>
     <t>Last Seen On</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
@@ -335,14 +239,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -439,7 +339,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -776,101 +676,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="25.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="32.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.19921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.3984375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.3984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -884,316 +787,4 @@
     </ext>
   </extLst>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="21.95" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.25" customWidth="1"/>
-    <col min="3" max="3" width="100.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>1004</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>1005</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>1006</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>1007</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>1017</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>1018</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>2003</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>2005</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>2008</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>2009</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>2011</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>2014</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>2016</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>2018</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>2025</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>2032</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>2034</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>2037</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>4010</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>4017</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>5006</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>5007</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>5011</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>